--- a/AplicacionesBanco.xlsx
+++ b/AplicacionesBanco.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProyectosNTT\PathCapacitacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A748057-37C6-4B87-A977-5F26EAFF233D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0B56CA-C52C-4A07-9540-1F7B997B3AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DB9A9BBE-2929-4FA8-BF12-267CB16A08E0}"/>
   </bookViews>
@@ -35720,7 +35720,6 @@
       <c r="FX158" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:FX124" xr:uid="{AAC5E0E0-4382-4DA6-82D2-DC1A061F4FD0}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:FX42">
     <sortCondition ref="B4:B42"/>
   </sortState>
